--- a/stocker_temp.xlsx
+++ b/stocker_temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POKORSSE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EADC2F-B13A-4348-9E91-9BDA00529CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41571921-F3E4-4D45-9A76-0F6B62B82744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feuille 1'!$A$1:$O$563</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3537" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="1126">
   <si>
     <t>Désignation:</t>
   </si>
@@ -3409,6 +3409,12 @@
   </si>
   <si>
     <t>Bechert Olivier</t>
+  </si>
+  <si>
+    <t>E720011</t>
+  </si>
+  <si>
+    <t>GILET DE SÉCURITE ER COULEUR JAUNE</t>
   </si>
 </sst>
 </file>
@@ -3710,7 +3716,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O562"/>
+  <dimension ref="A1:O563"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -23642,8 +23648,8 @@
       <c r="G542" s="5">
         <v>10</v>
       </c>
-      <c r="H542" s="4" t="s">
-        <v>51</v>
+      <c r="H542" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="I542" s="5" t="s">
         <v>10</v>
@@ -23662,33 +23668,33 @@
       </c>
     </row>
     <row r="543" spans="2:15" ht="15">
-      <c r="B543" s="4" t="s">
-        <v>996</v>
-      </c>
-      <c r="C543" s="4" t="s">
-        <v>997</v>
-      </c>
-      <c r="D543" s="4">
-        <v>0</v>
+      <c r="B543" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D543" s="5">
+        <v>5</v>
       </c>
       <c r="E543" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F543" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G543" s="5">
-        <v>15</v>
-      </c>
-      <c r="H543" s="4" t="s">
-        <v>51</v>
+        <v>10</v>
+      </c>
+      <c r="H543" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="I543" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J543" s="5"/>
-      <c r="K543" s="4" t="s">
-        <v>727</v>
+      <c r="K543" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="L543" s="5"/>
       <c r="M543" s="7"/>
@@ -23699,10 +23705,10 @@
     </row>
     <row r="544" spans="2:15" ht="15">
       <c r="B544" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D544" s="4">
         <v>0</v>
@@ -23716,8 +23722,8 @@
       <c r="G544" s="5">
         <v>15</v>
       </c>
-      <c r="H544" s="4" t="s">
-        <v>51</v>
+      <c r="H544" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="I544" s="5" t="s">
         <v>10</v>
@@ -23733,18 +23739,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="2:15" ht="15" hidden="1">
+    <row r="545" spans="2:15" ht="15">
       <c r="B545" s="4" t="s">
-        <v>1062</v>
+        <v>998</v>
       </c>
       <c r="C545" s="4" t="s">
-        <v>808</v>
+        <v>999</v>
       </c>
       <c r="D545" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E545" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F545" s="5">
         <v>5</v>
@@ -23752,36 +23758,32 @@
       <c r="G545" s="5">
         <v>15</v>
       </c>
-      <c r="H545" s="4" t="s">
-        <v>67</v>
+      <c r="H545" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="I545" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J545" s="4" t="s">
-        <v>1063</v>
-      </c>
+      <c r="J545" s="5"/>
       <c r="K545" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L545" s="5"/>
       <c r="M545" s="7"/>
-      <c r="N545" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N545" s="6"/>
       <c r="O545" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="546" spans="2:15" ht="15" hidden="1">
       <c r="B546" s="4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>263</v>
+        <v>808</v>
       </c>
       <c r="D546" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -23793,19 +23795,21 @@
         <v>15</v>
       </c>
       <c r="H546" s="4" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="I546" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J546" s="5"/>
+      <c r="J546" s="4" t="s">
+        <v>1063</v>
+      </c>
       <c r="K546" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L546" s="5"/>
       <c r="M546" s="7"/>
       <c r="N546" s="6" t="s">
-        <v>1084</v>
+        <v>17</v>
       </c>
       <c r="O546" s="6" t="s">
         <v>12</v>
@@ -23813,13 +23817,13 @@
     </row>
     <row r="547" spans="2:15" ht="15" hidden="1">
       <c r="B547" s="4" t="s">
-        <v>27</v>
+        <v>1064</v>
       </c>
       <c r="C547" s="4" t="s">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="D547" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E547" s="5">
         <v>1</v>
@@ -23843,24 +23847,24 @@
       <c r="L547" s="5"/>
       <c r="M547" s="7"/>
       <c r="N547" s="6" t="s">
-        <v>17</v>
+        <v>1084</v>
       </c>
       <c r="O547" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="2:15" ht="15">
+    <row r="548" spans="2:15" ht="15" hidden="1">
       <c r="B548" s="4" t="s">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1001</v>
+        <v>28</v>
       </c>
       <c r="D548" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E548" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F548" s="5">
         <v>5</v>
@@ -23869,34 +23873,36 @@
         <v>15</v>
       </c>
       <c r="H548" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I548" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J548" s="5"/>
       <c r="K548" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L548" s="5"/>
       <c r="M548" s="7"/>
-      <c r="N548" s="6"/>
+      <c r="N548" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O548" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="2:15" ht="15" hidden="1">
+    <row r="549" spans="2:15" ht="15">
       <c r="B549" s="4" t="s">
-        <v>1066</v>
+        <v>1000</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>933</v>
+        <v>1001</v>
       </c>
       <c r="D549" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E549" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F549" s="5">
         <v>5</v>
@@ -23904,7 +23910,7 @@
       <c r="G549" s="5">
         <v>15</v>
       </c>
-      <c r="H549" s="4" t="s">
+      <c r="H549" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I549" s="5" t="s">
@@ -23912,29 +23918,27 @@
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L549" s="5"/>
       <c r="M549" s="7"/>
-      <c r="N549" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="N549" s="6"/>
       <c r="O549" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="550" spans="2:15" ht="15">
+    <row r="550" spans="2:15" ht="15" hidden="1">
       <c r="B550" s="4" t="s">
-        <v>728</v>
+        <v>1066</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>729</v>
+        <v>933</v>
       </c>
       <c r="D550" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E550" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F550" s="5">
         <v>5</v>
@@ -23943,34 +23947,36 @@
         <v>15</v>
       </c>
       <c r="H550" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I550" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J550" s="5"/>
       <c r="K550" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L550" s="5"/>
       <c r="M550" s="7"/>
-      <c r="N550" s="6"/>
+      <c r="N550" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="O550" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="551" spans="2:15" ht="15" hidden="1">
+    <row r="551" spans="2:15" ht="15">
       <c r="B551" s="4" t="s">
-        <v>1067</v>
+        <v>728</v>
       </c>
       <c r="C551" s="4" t="s">
-        <v>1068</v>
+        <v>729</v>
       </c>
       <c r="D551" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E551" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F551" s="5">
         <v>5</v>
@@ -23978,37 +23984,35 @@
       <c r="G551" s="5">
         <v>15</v>
       </c>
-      <c r="H551" s="4" t="s">
+      <c r="H551" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I551" s="5" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J551" s="5"/>
       <c r="K551" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L551" s="5"/>
       <c r="M551" s="7"/>
-      <c r="N551" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N551" s="6"/>
       <c r="O551" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="552" spans="2:15" ht="15">
+    <row r="552" spans="2:15" ht="15" hidden="1">
       <c r="B552" s="4" t="s">
-        <v>730</v>
+        <v>1067</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>731</v>
+        <v>1068</v>
       </c>
       <c r="D552" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E552" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F552" s="5">
         <v>5</v>
@@ -24017,30 +24021,32 @@
         <v>15</v>
       </c>
       <c r="H552" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I552" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J552" s="5"/>
       <c r="K552" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L552" s="5"/>
       <c r="M552" s="7"/>
-      <c r="N552" s="6"/>
+      <c r="N552" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O552" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="2:15" ht="15">
-      <c r="B553" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="C553" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="D553" s="5">
+      <c r="B553" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D553" s="4">
         <v>0</v>
       </c>
       <c r="E553" s="5">
@@ -24053,13 +24059,13 @@
         <v>15</v>
       </c>
       <c r="H553" s="5" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I553" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J553" s="5"/>
-      <c r="K553" s="5" t="s">
+      <c r="K553" s="4" t="s">
         <v>727</v>
       </c>
       <c r="L553" s="5"/>
@@ -24071,13 +24077,13 @@
     </row>
     <row r="554" spans="2:15" ht="15">
       <c r="B554" s="5" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D554" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E554" s="5">
         <v>100</v>
@@ -24089,7 +24095,7 @@
         <v>15</v>
       </c>
       <c r="H554" s="5" t="s">
-        <v>736</v>
+        <v>2</v>
       </c>
       <c r="I554" s="5" t="s">
         <v>10</v>
@@ -24105,18 +24111,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="555" spans="2:15" ht="15" hidden="1">
-      <c r="B555" s="4">
-        <v>3353213</v>
-      </c>
-      <c r="C555" s="4" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D555" s="4">
+    <row r="555" spans="2:15" ht="15">
+      <c r="B555" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D555" s="5">
         <v>1</v>
       </c>
       <c r="E555" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F555" s="5">
         <v>5</v>
@@ -24124,34 +24130,32 @@
       <c r="G555" s="5">
         <v>15</v>
       </c>
-      <c r="H555" s="4" t="s">
-        <v>2</v>
+      <c r="H555" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="I555" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J555" s="5"/>
-      <c r="K555" s="4" t="s">
-        <v>11</v>
+      <c r="K555" s="5" t="s">
+        <v>727</v>
       </c>
       <c r="L555" s="5"/>
       <c r="M555" s="7"/>
-      <c r="N555" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="N555" s="6"/>
       <c r="O555" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="556" spans="2:15" ht="15" hidden="1">
-      <c r="B556" s="4" t="s">
-        <v>124</v>
+      <c r="B556" s="4">
+        <v>3353213</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>125</v>
+        <v>1037</v>
       </c>
       <c r="D556" s="4">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -24175,7 +24179,7 @@
       <c r="L556" s="5"/>
       <c r="M556" s="7"/>
       <c r="N556" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O556" s="6" t="s">
         <v>12</v>
@@ -24183,13 +24187,13 @@
     </row>
     <row r="557" spans="2:15" ht="15" hidden="1">
       <c r="B557" s="4" t="s">
-        <v>1069</v>
+        <v>124</v>
       </c>
       <c r="C557" s="4" t="s">
-        <v>1070</v>
+        <v>125</v>
       </c>
       <c r="D557" s="4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="E557" s="5">
         <v>1</v>
@@ -24213,7 +24217,7 @@
       <c r="L557" s="5"/>
       <c r="M557" s="7"/>
       <c r="N557" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O557" s="6" t="s">
         <v>12</v>
@@ -24221,13 +24225,13 @@
     </row>
     <row r="558" spans="2:15" ht="15" hidden="1">
       <c r="B558" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>949</v>
+        <v>1070</v>
       </c>
       <c r="D558" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -24239,21 +24243,19 @@
         <v>15</v>
       </c>
       <c r="H558" s="4" t="s">
-        <v>736</v>
+        <v>2</v>
       </c>
       <c r="I558" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J558" s="4" t="s">
-        <v>1072</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J558" s="5"/>
       <c r="K558" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L558" s="5"/>
       <c r="M558" s="7"/>
       <c r="N558" s="6" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="O558" s="6" t="s">
         <v>12</v>
@@ -24261,10 +24263,10 @@
     </row>
     <row r="559" spans="2:15" ht="15" hidden="1">
       <c r="B559" s="4" t="s">
-        <v>810</v>
+        <v>1071</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>811</v>
+        <v>949</v>
       </c>
       <c r="D559" s="4">
         <v>1</v>
@@ -24279,13 +24281,13 @@
         <v>15</v>
       </c>
       <c r="H559" s="4" t="s">
-        <v>2</v>
+        <v>736</v>
       </c>
       <c r="I559" s="5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J559" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="K559" s="4" t="s">
         <v>11</v>
@@ -24293,24 +24295,24 @@
       <c r="L559" s="5"/>
       <c r="M559" s="7"/>
       <c r="N559" s="6" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="O559" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="560" spans="2:15" ht="15">
+    <row r="560" spans="2:15" ht="15" hidden="1">
       <c r="B560" s="4" t="s">
-        <v>737</v>
+        <v>810</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>738</v>
+        <v>811</v>
       </c>
       <c r="D560" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E560" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F560" s="5">
         <v>5</v>
@@ -24319,34 +24321,38 @@
         <v>15</v>
       </c>
       <c r="H560" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I560" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J560" s="5"/>
+      <c r="J560" s="4" t="s">
+        <v>1073</v>
+      </c>
       <c r="K560" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L560" s="5"/>
       <c r="M560" s="7"/>
-      <c r="N560" s="6"/>
+      <c r="N560" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="O560" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="561" spans="2:15" ht="15" hidden="1">
+    <row r="561" spans="2:15" ht="15">
       <c r="B561" s="4" t="s">
-        <v>1075</v>
+        <v>737</v>
       </c>
       <c r="C561" s="4" t="s">
-        <v>1076</v>
+        <v>738</v>
       </c>
       <c r="D561" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E561" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F561" s="5">
         <v>5</v>
@@ -24355,36 +24361,34 @@
         <v>15</v>
       </c>
       <c r="H561" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I561" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J561" s="5"/>
       <c r="K561" s="4" t="s">
-        <v>11</v>
+        <v>727</v>
       </c>
       <c r="L561" s="5"/>
       <c r="M561" s="7"/>
-      <c r="N561" s="6" t="s">
-        <v>443</v>
-      </c>
+      <c r="N561" s="6"/>
       <c r="O561" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="562" spans="2:15" ht="15">
+    <row r="562" spans="2:15" ht="15" hidden="1">
       <c r="B562" s="4" t="s">
-        <v>739</v>
+        <v>1075</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>740</v>
+        <v>1076</v>
       </c>
       <c r="D562" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E562" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F562" s="5">
         <v>5</v>
@@ -24393,31 +24397,69 @@
         <v>15</v>
       </c>
       <c r="H562" s="4" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I562" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="4" t="s">
-        <v>727</v>
+        <v>11</v>
       </c>
       <c r="L562" s="5"/>
       <c r="M562" s="7"/>
-      <c r="N562" s="6"/>
+      <c r="N562" s="6" t="s">
+        <v>443</v>
+      </c>
       <c r="O562" s="6" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="563" spans="2:15" ht="15">
+      <c r="B563" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="C563" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="D563" s="4">
+        <v>0</v>
+      </c>
+      <c r="E563" s="5">
+        <v>100</v>
+      </c>
+      <c r="F563" s="5">
+        <v>5</v>
+      </c>
+      <c r="G563" s="5">
+        <v>15</v>
+      </c>
+      <c r="H563" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I563" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J563" s="5"/>
+      <c r="K563" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="L563" s="5"/>
+      <c r="M563" s="7"/>
+      <c r="N563" s="6"/>
+      <c r="O563" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O562" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:O563" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="10">
       <filters>
         <filter val="ER-MP"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O562">
-      <sortCondition ref="B1:B562"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A346:O563">
+      <sortCondition ref="B1:B563"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
